--- a/Employee_Reports_wi48/Edwin Balakid Tegli Q0157.xlsx
+++ b/Employee_Reports_wi48/Edwin Balakid Tegli Q0157.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-129</v>
+        <v>-132</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -846,9 +846,21 @@
           <t>Procedure For Handling New or Unfamilliar Task (SOPs)</t>
         </is>
       </c>
-      <c r="C9" s="4" t="inlineStr"/>
-      <c r="D9" s="4" t="inlineStr"/>
-      <c r="E9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>IMS</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>LSME-IMS-SOP-022</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>SOP</t>
+        </is>
+      </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
           <t>29-May-2025</t>
@@ -860,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-45</v>
+        <v>-48</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -909,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="5" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
@@ -946,11 +958,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1191,7 +1203,7 @@
         </is>
       </c>
       <c r="E3" s="3" t="n">
-        <v>7650</v>
+        <v>7647</v>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
